--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-09-29 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:03</t>
+    <t xml:space="preserve">2026-09-29 18:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -501,10 +501,10 @@
         <v>0.07</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>35.08</v>
+        <v>35.07</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>35</v>
+        <v>35.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:36</t>
+    <t xml:space="preserve">2026-10-05 04:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -501,7 +501,7 @@
         <v>0.07</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>35.07</v>
+        <v>35.08</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>35.01</v>
